--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run4/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run4/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,0,1,1</t>
-  </si>
-  <si>
-    <t>0.9265,0.0234,0.0097,0.0220</t>
-  </si>
-  <si>
-    <t>0.0593,0.0020,0.0007,0.9768</t>
-  </si>
-  <si>
-    <t>0.8769,0.0177,0.0083,0.0964</t>
-  </si>
-  <si>
-    <t>0.0703,0.0074,0.0065,0.9705</t>
-  </si>
-  <si>
-    <t>0.9977,0.0006,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9919,0.0049,0.0011,0.0005</t>
-  </si>
-  <si>
-    <t>0.9986,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9958,0.0015,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9890,0.0143,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9987,0.0001,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9986,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.6764,0.0295,0.4022,0.0052</t>
-  </si>
-  <si>
-    <t>0.5597,0.0428,0.5229,0.0087</t>
-  </si>
-  <si>
-    <t>0.4950,0.0217,0.6586,0.0016</t>
-  </si>
-  <si>
-    <t>0.3441,0.0825,0.6401,0.0304</t>
-  </si>
-  <si>
-    <t>0.8453,0.0309,0.1557,0.0032</t>
-  </si>
-  <si>
-    <t>0.0185,0.9701,0.0145,0.0012</t>
-  </si>
-  <si>
-    <t>0.0196,0.9723,0.0169,0.0004</t>
-  </si>
-  <si>
-    <t>0.2362,0.7996,0.0170,0.0019</t>
-  </si>
-  <si>
-    <t>0.0166,0.9750,0.0019,0.0013</t>
-  </si>
-  <si>
-    <t>0.0078,0.9850,0.0068,0.0004</t>
-  </si>
-  <si>
-    <t>0.7550,0.0037,0.2674,0.0185</t>
-  </si>
-  <si>
-    <t>0.6011,0.0041,0.6073,0.0014</t>
-  </si>
-  <si>
-    <t>0.0058,0.0034,0.9912,0.0011</t>
-  </si>
-  <si>
-    <t>0.2662,0.0131,0.8117,0.0021</t>
-  </si>
-  <si>
-    <t>0.0284,0.0177,0.9625,0.0009</t>
-  </si>
-  <si>
-    <t>0.0307,0.0027,0.9731,0.0011</t>
-  </si>
-  <si>
-    <t>0.0212,0.0025,0.9716,0.0058</t>
-  </si>
-  <si>
-    <t>0.4763,0.3256,0.1341,0.0012</t>
-  </si>
-  <si>
-    <t>0.2663,0.1551,0.6618,0.0043</t>
-  </si>
-  <si>
-    <t>0.0002,0.0036,0.9972,0.0063</t>
-  </si>
-  <si>
-    <t>0.0131,0.8703,0.5677,0.0012</t>
-  </si>
-  <si>
-    <t>0.8836,0.0570,0.0372,0.0236</t>
-  </si>
-  <si>
-    <t>0.9117,0.0277,0.0585,0.0075</t>
-  </si>
-  <si>
-    <t>0.6048,0.5112,0.0112,0.0018</t>
-  </si>
-  <si>
-    <t>0.1342,0.8602,0.0621,0.0023</t>
-  </si>
-  <si>
-    <t>0.0509,0.5040,0.6474,0.0370</t>
-  </si>
-  <si>
-    <t>0.0370,0.0030,0.9653,0.0034</t>
-  </si>
-  <si>
-    <t>0.0865,0.0701,0.8421,0.0546</t>
-  </si>
-  <si>
-    <t>0.1523,0.0018,0.8766,0.0072</t>
-  </si>
-  <si>
-    <t>0.0101,0.1426,0.9672,0.0007</t>
-  </si>
-  <si>
-    <t>0.0076,0.9486,0.0592,0.0246</t>
-  </si>
-  <si>
-    <t>0.0136,0.1457,0.9394,0.0057</t>
-  </si>
-  <si>
-    <t>0.1925,0.2896,0.0193,0.7781</t>
-  </si>
-  <si>
-    <t>0.0608,0.9269,0.0119,0.0054</t>
-  </si>
-  <si>
-    <t>0.0178,0.9041,0.3560,0.0028</t>
-  </si>
-  <si>
-    <t>0.0065,0.9686,0.1803,0.0041</t>
-  </si>
-  <si>
-    <t>0.0020,0.1494,0.9868,0.0007</t>
-  </si>
-  <si>
-    <t>0.0199,0.1794,0.9626,0.0004</t>
-  </si>
-  <si>
-    <t>0.1995,0.0018,0.9141,0.0005</t>
-  </si>
-  <si>
-    <t>0.0103,0.0014,0.9891,0.0010</t>
-  </si>
-  <si>
-    <t>0.0213,0.0296,0.9473,0.0134</t>
-  </si>
-  <si>
-    <t>0.0120,0.0035,0.9817,0.0021</t>
-  </si>
-  <si>
-    <t>0.9620,0.0365,0.0062,0.0011</t>
-  </si>
-  <si>
-    <t>0.9844,0.0068,0.0024,0.0018</t>
-  </si>
-  <si>
-    <t>0.9620,0.0257,0.0099,0.0019</t>
-  </si>
-  <si>
-    <t>0.0095,0.0736,0.9764,0.0062</t>
-  </si>
-  <si>
-    <t>0.9926,0.0043,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.9949,0.0026,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9448,0.0657,0.0027,0.0021</t>
-  </si>
-  <si>
-    <t>0.0012,0.7011,0.9754,0.0006</t>
-  </si>
-  <si>
-    <t>0.0036,0.0396,0.9861,0.0025</t>
-  </si>
-  <si>
-    <t>0.0057,0.0071,0.9862,0.0037</t>
-  </si>
-  <si>
-    <t>0.0003,0.9511,0.9765,0.0001</t>
-  </si>
-  <si>
-    <t>0.0034,0.0024,0.9960,0.0001</t>
-  </si>
-  <si>
-    <t>0.0530,0.6549,0.3304,0.0011</t>
-  </si>
-  <si>
-    <t>0.0053,0.9866,0.0032,0.0011</t>
-  </si>
-  <si>
-    <t>0.8004,0.0294,0.2303,0.0065</t>
-  </si>
-  <si>
-    <t>0.2505,0.1448,0.6736,0.0039</t>
-  </si>
-  <si>
-    <t>0.0085,0.0448,0.9766,0.0066</t>
-  </si>
-  <si>
-    <t>0.0015,0.8102,0.9264,0.0001</t>
-  </si>
-  <si>
-    <t>0.0115,0.1803,0.9611,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.9842,0.4874,0.0002</t>
-  </si>
-  <si>
-    <t>0.0024,0.8101,0.9561,0.0011</t>
-  </si>
-  <si>
-    <t>0.0033,0.0009,0.0351,0.9909</t>
-  </si>
-  <si>
-    <t>0.0082,0.0010,0.0002,0.9973</t>
-  </si>
-  <si>
-    <t>0.0616,0.0001,0.0001,0.9873</t>
-  </si>
-  <si>
-    <t>0.0372,0.0025,0.0047,0.9797</t>
-  </si>
-  <si>
-    <t>0.0308,0.0037,0.0111,0.9779</t>
-  </si>
-  <si>
-    <t>0.0099,0.0035,0.0001,0.9956</t>
-  </si>
-  <si>
-    <t>0.0025,0.9716,0.2535,0.0014</t>
-  </si>
-  <si>
-    <t>0.0028,0.5737,0.9690,0.0003</t>
-  </si>
-  <si>
-    <t>0.0121,0.2445,0.9550,0.0020</t>
-  </si>
-  <si>
-    <t>0.0104,0.5670,0.9353,0.0024</t>
-  </si>
-  <si>
-    <t>0.0009,0.8248,0.9513,0.0001</t>
-  </si>
-  <si>
-    <t>0.0031,0.7146,0.9330,0.0004</t>
-  </si>
-  <si>
-    <t>0.9927,0.0045,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.9810,0.0232,0.0014,0.0005</t>
-  </si>
-  <si>
-    <t>0.9790,0.0274,0.0022,0.0003</t>
-  </si>
-  <si>
-    <t>0.9975,0.0007,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9958,0.0031,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9963,0.0022,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9857,0.0129,0.0016,0.0007</t>
-  </si>
-  <si>
-    <t>0.9817,0.0158,0.0035,0.0005</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9964,0.0014,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9969,0.0014,0.0002,0.0002</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.8746,0.0309,0.0074,0.0646</t>
+  </si>
+  <si>
+    <t>0.0505,0.0039,0.0009,0.9819</t>
+  </si>
+  <si>
+    <t>0.5971,0.0735,0.0026,0.2825</t>
+  </si>
+  <si>
+    <t>0.0265,0.0230,0.0036,0.9849</t>
+  </si>
+  <si>
+    <t>0.9978,0.0017,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9952,0.0022,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9930,0.0036,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.9873,0.0123,0.0016,0.0003</t>
+  </si>
+  <si>
+    <t>0.9959,0.0024,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9917,0.0130,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.8204,0.0171,0.2271,0.0048</t>
+  </si>
+  <si>
+    <t>0.2097,0.0240,0.8288,0.0059</t>
+  </si>
+  <si>
+    <t>0.3184,0.0571,0.6535,0.0010</t>
+  </si>
+  <si>
+    <t>0.0965,0.0162,0.9074,0.0028</t>
+  </si>
+  <si>
+    <t>0.8708,0.0090,0.1185,0.0091</t>
+  </si>
+  <si>
+    <t>0.0077,0.9861,0.0035,0.0006</t>
+  </si>
+  <si>
+    <t>0.0019,0.9916,0.0219,0.0005</t>
+  </si>
+  <si>
+    <t>0.2487,0.7882,0.0247,0.0039</t>
+  </si>
+  <si>
+    <t>0.0737,0.9238,0.0054,0.0042</t>
+  </si>
+  <si>
+    <t>0.0053,0.9888,0.0042,0.0003</t>
+  </si>
+  <si>
+    <t>0.6037,0.0099,0.4830,0.0159</t>
+  </si>
+  <si>
+    <t>0.6789,0.0113,0.4364,0.0053</t>
+  </si>
+  <si>
+    <t>0.0691,0.0031,0.9569,0.0007</t>
+  </si>
+  <si>
+    <t>0.1472,0.0640,0.8189,0.0117</t>
+  </si>
+  <si>
+    <t>0.1182,0.0033,0.9374,0.0003</t>
+  </si>
+  <si>
+    <t>0.2435,0.0064,0.8128,0.0078</t>
+  </si>
+  <si>
+    <t>0.0133,0.0007,0.9889,0.0006</t>
+  </si>
+  <si>
+    <t>0.7962,0.3050,0.0057,0.0008</t>
+  </si>
+  <si>
+    <t>0.7989,0.0229,0.2229,0.0087</t>
+  </si>
+  <si>
+    <t>0.0017,0.0123,0.9900,0.0151</t>
+  </si>
+  <si>
+    <t>0.1768,0.6948,0.2110,0.0054</t>
+  </si>
+  <si>
+    <t>0.8843,0.0381,0.0293,0.0396</t>
+  </si>
+  <si>
+    <t>0.8221,0.0747,0.1159,0.0154</t>
+  </si>
+  <si>
+    <t>0.7861,0.2435,0.0254,0.0011</t>
+  </si>
+  <si>
+    <t>0.0396,0.8890,0.3198,0.0029</t>
+  </si>
+  <si>
+    <t>0.0455,0.7335,0.4013,0.0668</t>
+  </si>
+  <si>
+    <t>0.1327,0.0298,0.8830,0.0070</t>
+  </si>
+  <si>
+    <t>0.0882,0.0738,0.9028,0.0085</t>
+  </si>
+  <si>
+    <t>0.0242,0.0028,0.9144,0.0832</t>
+  </si>
+  <si>
+    <t>0.0168,0.1109,0.9563,0.0012</t>
+  </si>
+  <si>
+    <t>0.0259,0.8477,0.1566,0.0055</t>
+  </si>
+  <si>
+    <t>0.0045,0.0677,0.9747,0.0084</t>
+  </si>
+  <si>
+    <t>0.2843,0.2566,0.0259,0.6370</t>
+  </si>
+  <si>
+    <t>0.0188,0.9560,0.0090,0.0310</t>
+  </si>
+  <si>
+    <t>0.0057,0.9428,0.2745,0.0039</t>
+  </si>
+  <si>
+    <t>0.0024,0.9828,0.0932,0.0054</t>
+  </si>
+  <si>
+    <t>0.0662,0.0338,0.9255,0.0094</t>
+  </si>
+  <si>
+    <t>0.0122,0.0382,0.9833,0.0001</t>
+  </si>
+  <si>
+    <t>0.0187,0.0019,0.9636,0.0158</t>
+  </si>
+  <si>
+    <t>0.0402,0.0060,0.9535,0.0057</t>
+  </si>
+  <si>
+    <t>0.0016,0.0022,0.9954,0.0012</t>
+  </si>
+  <si>
+    <t>0.0043,0.0139,0.9875,0.0007</t>
+  </si>
+  <si>
+    <t>0.9326,0.0826,0.0092,0.0016</t>
+  </si>
+  <si>
+    <t>0.9597,0.0247,0.0144,0.0023</t>
+  </si>
+  <si>
+    <t>0.9712,0.0130,0.0101,0.0029</t>
+  </si>
+  <si>
+    <t>0.0067,0.0586,0.9807,0.0069</t>
+  </si>
+  <si>
+    <t>0.9937,0.0015,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.9886,0.0107,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.9875,0.0136,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.0061,0.1428,0.9715,0.0027</t>
+  </si>
+  <si>
+    <t>0.0062,0.1953,0.9825,0.0011</t>
+  </si>
+  <si>
+    <t>0.0051,0.0029,0.9901,0.0014</t>
+  </si>
+  <si>
+    <t>0.0003,0.9369,0.9633,0.0001</t>
+  </si>
+  <si>
+    <t>0.0033,0.0043,0.9949,0.0001</t>
+  </si>
+  <si>
+    <t>0.0490,0.8541,0.1376,0.0019</t>
+  </si>
+  <si>
+    <t>0.0092,0.9785,0.0078,0.0009</t>
+  </si>
+  <si>
+    <t>0.8940,0.0486,0.0505,0.0069</t>
+  </si>
+  <si>
+    <t>0.8670,0.0543,0.0978,0.0081</t>
+  </si>
+  <si>
+    <t>0.0065,0.2016,0.9270,0.0057</t>
+  </si>
+  <si>
+    <t>0.0016,0.8050,0.9622,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.7954,0.9641,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9920,0.6827,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.9221,0.8453,0.0002</t>
+  </si>
+  <si>
+    <t>0.0409,0.0029,0.0134,0.9701</t>
+  </si>
+  <si>
+    <t>0.0135,0.0006,0.0000,0.9967</t>
+  </si>
+  <si>
+    <t>0.0114,0.0016,0.0011,0.9945</t>
+  </si>
+  <si>
+    <t>0.0855,0.0010,0.0015,0.9690</t>
+  </si>
+  <si>
+    <t>0.1782,0.0009,0.0039,0.9229</t>
+  </si>
+  <si>
+    <t>0.0081,0.0041,0.0006,0.9952</t>
+  </si>
+  <si>
+    <t>0.0006,0.9633,0.8283,0.0002</t>
+  </si>
+  <si>
+    <t>0.0046,0.6484,0.9648,0.0006</t>
+  </si>
+  <si>
+    <t>0.0223,0.5739,0.8169,0.0024</t>
+  </si>
+  <si>
+    <t>0.0153,0.2491,0.9369,0.0025</t>
+  </si>
+  <si>
+    <t>0.0010,0.8240,0.9607,0.0001</t>
+  </si>
+  <si>
+    <t>0.0121,0.1184,0.9606,0.0012</t>
+  </si>
+  <si>
+    <t>0.9963,0.0025,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9713,0.0413,0.0025,0.0004</t>
+  </si>
+  <si>
+    <t>0.9729,0.0323,0.0028,0.0010</t>
+  </si>
+  <si>
+    <t>0.9976,0.0003,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9927,0.0024,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9986,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9695,0.0310,0.0030,0.0019</t>
+  </si>
+  <si>
+    <t>0.9672,0.0450,0.0037,0.0005</t>
+  </si>
+  <si>
+    <t>0.9985,0.0001,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9980,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9974,0.0007,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9977,0.0004,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9987,0.0003,0.0000,0.0002</t>
   </si>
   <si>
     <t>0.9986,0.0002,0.0000,0.0002</t>
   </si>
   <si>
-    <t>0.9944,0.0020,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0059,0.0015,0.9893,0.0029</t>
-  </si>
-  <si>
-    <t>0.0230,0.0053,0.9744,0.0013</t>
-  </si>
-  <si>
-    <t>0.6241,0.1001,0.2478,0.1254</t>
-  </si>
-  <si>
-    <t>0.1688,0.0019,0.9013,0.0024</t>
-  </si>
-  <si>
-    <t>0.2106,0.8338,0.0084,0.0015</t>
-  </si>
-  <si>
-    <t>0.0217,0.9646,0.0051,0.0027</t>
-  </si>
-  <si>
-    <t>0.1665,0.8591,0.0135,0.0026</t>
-  </si>
-  <si>
-    <t>0.2646,0.7939,0.0127,0.0027</t>
-  </si>
-  <si>
-    <t>0.1221,0.8734,0.0178,0.0063</t>
-  </si>
-  <si>
-    <t>0.0082,0.9818,0.0022,0.0013</t>
-  </si>
-  <si>
-    <t>0.9267,0.0862,0.0088,0.0023</t>
-  </si>
-  <si>
-    <t>0.5642,0.1452,0.3629,0.0168</t>
-  </si>
-  <si>
-    <t>0.3997,0.0186,0.6890,0.0099</t>
-  </si>
-  <si>
-    <t>0.8783,0.0268,0.0425,0.0123</t>
-  </si>
-  <si>
-    <t>0.7660,0.0175,0.3148,0.0067</t>
-  </si>
-  <si>
-    <t>0.4181,0.0734,0.1304,0.5585</t>
-  </si>
-  <si>
-    <t>0.0138,0.9614,0.1236,0.0022</t>
-  </si>
-  <si>
-    <t>0.0087,0.9704,0.0134,0.0140</t>
-  </si>
-  <si>
-    <t>0.0561,0.8856,0.0170,0.1390</t>
-  </si>
-  <si>
-    <t>0.0010,0.7733,0.9693,0.0006</t>
-  </si>
-  <si>
-    <t>0.0323,0.9686,0.0276,0.0002</t>
-  </si>
-  <si>
-    <t>0.4484,0.4304,0.0669,0.0003</t>
-  </si>
-  <si>
-    <t>0.6084,0.4728,0.0166,0.0023</t>
-  </si>
-  <si>
-    <t>0.9896,0.0058,0.0020,0.0005</t>
-  </si>
-  <si>
-    <t>0.9684,0.0100,0.0172,0.0023</t>
-  </si>
-  <si>
-    <t>0.9903,0.0027,0.0020,0.0015</t>
-  </si>
-  <si>
-    <t>0.9935,0.0008,0.0008,0.0017</t>
-  </si>
-  <si>
-    <t>0.9876,0.0065,0.0034,0.0011</t>
-  </si>
-  <si>
-    <t>0.9836,0.0045,0.0056,0.0020</t>
-  </si>
-  <si>
-    <t>0.9926,0.0006,0.0005,0.0028</t>
-  </si>
-  <si>
-    <t>0.9952,0.0007,0.0004,0.0011</t>
-  </si>
-  <si>
-    <t>0.0078,0.6324,0.9214,0.0021</t>
-  </si>
-  <si>
-    <t>0.0060,0.6786,0.8532,0.0001</t>
-  </si>
-  <si>
-    <t>0.0371,0.4241,0.7849,0.0024</t>
-  </si>
-  <si>
-    <t>0.0114,0.0600,0.9704,0.0004</t>
-  </si>
-  <si>
-    <t>0.4110,0.4191,0.0435,0.2080</t>
-  </si>
-  <si>
-    <t>0.2027,0.0211,0.8037,0.0369</t>
-  </si>
-  <si>
-    <t>0.1299,0.0007,0.9341,0.0022</t>
-  </si>
-  <si>
-    <t>0.6240,0.2379,0.1693,0.0107</t>
-  </si>
-  <si>
-    <t>0.0854,0.0082,0.0038,0.9637</t>
-  </si>
-  <si>
-    <t>0.0021,0.0002,0.0004,0.9988</t>
-  </si>
-  <si>
-    <t>0.0123,0.0053,0.0004,0.9946</t>
-  </si>
-  <si>
-    <t>0.1226,0.0005,0.0009,0.9661</t>
-  </si>
-  <si>
-    <t>0.0082,0.5097,0.8620,0.0102</t>
-  </si>
-  <si>
-    <t>0.9850,0.0052,0.0016,0.0023</t>
-  </si>
-  <si>
-    <t>0.0791,0.8987,0.0166,0.0186</t>
-  </si>
-  <si>
-    <t>0.9950,0.0016,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.5306,0.5381,0.0226,0.0078</t>
-  </si>
-  <si>
-    <t>0.9850,0.0054,0.0032,0.0014</t>
-  </si>
-  <si>
-    <t>0.4261,0.0032,0.0055,0.7610</t>
-  </si>
-  <si>
-    <t>0.9912,0.0044,0.0014,0.0007</t>
-  </si>
-  <si>
-    <t>0.0008,0.3541,0.9887,0.0007</t>
-  </si>
-  <si>
-    <t>0.9799,0.0018,0.0019,0.0111</t>
-  </si>
-  <si>
-    <t>0.9606,0.0018,0.0045,0.0191</t>
-  </si>
-  <si>
-    <t>0.4676,0.4465,0.0084,0.0579</t>
-  </si>
-  <si>
-    <t>0.9452,0.0192,0.0206,0.0017</t>
-  </si>
-  <si>
-    <t>0.9358,0.0410,0.0119,0.0021</t>
-  </si>
-  <si>
-    <t>0.3999,0.4857,0.0365,0.1007</t>
-  </si>
-  <si>
-    <t>0.7789,0.1208,0.1002,0.0023</t>
-  </si>
-  <si>
-    <t>0.9585,0.0271,0.0049,0.0016</t>
-  </si>
-  <si>
-    <t>0.9955,0.0014,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.9933,0.0043,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9967,0.0006,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9938,0.0012,0.0004,0.0016</t>
-  </si>
-  <si>
-    <t>0.9847,0.0054,0.0023,0.0025</t>
-  </si>
-  <si>
-    <t>0.9957,0.0012,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9951,0.0005,0.0001,0.0017</t>
-  </si>
-  <si>
-    <t>0.9947,0.0018,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.8527,0.1483,0.0040,0.0086</t>
-  </si>
-  <si>
-    <t>0.5123,0.5838,0.0156,0.0006</t>
-  </si>
-  <si>
-    <t>0.4053,0.7330,0.0052,0.0003</t>
-  </si>
-  <si>
-    <t>0.9016,0.0445,0.0556,0.0145</t>
-  </si>
-  <si>
-    <t>0.9651,0.0301,0.0069,0.0015</t>
-  </si>
-  <si>
-    <t>0.9587,0.0275,0.0035,0.0035</t>
-  </si>
-  <si>
-    <t>0.9862,0.0073,0.0021,0.0008</t>
-  </si>
-  <si>
-    <t>0.8949,0.1803,0.0037,0.0008</t>
-  </si>
-  <si>
-    <t>0.0021,0.1296,0.9913,0.0003</t>
-  </si>
-  <si>
-    <t>0.9579,0.0237,0.0116,0.0057</t>
-  </si>
-  <si>
-    <t>0.0042,0.0076,0.9918,0.0002</t>
-  </si>
-  <si>
-    <t>0.0409,0.0187,0.9430,0.0088</t>
-  </si>
-  <si>
-    <t>0.0591,0.0067,0.9427,0.0023</t>
-  </si>
-  <si>
-    <t>0.0174,0.0142,0.9800,0.0007</t>
-  </si>
-  <si>
-    <t>0.0453,0.0776,0.9015,0.0046</t>
-  </si>
-  <si>
-    <t>0.0100,0.0111,0.9808,0.0029</t>
-  </si>
-  <si>
-    <t>0.0083,0.0112,0.9885,0.0003</t>
-  </si>
-  <si>
-    <t>0.3614,0.0064,0.8110,0.0012</t>
-  </si>
-  <si>
-    <t>0.0335,0.0099,0.9627,0.0033</t>
-  </si>
-  <si>
-    <t>0.8318,0.0267,0.1621,0.0075</t>
-  </si>
-  <si>
-    <t>0.4188,0.1280,0.4856,0.0098</t>
-  </si>
-  <si>
-    <t>0.1041,0.4651,0.4988,0.0051</t>
-  </si>
-  <si>
-    <t>0.7007,0.0560,0.2842,0.0026</t>
-  </si>
-  <si>
-    <t>0.8877,0.0133,0.0833,0.0120</t>
-  </si>
-  <si>
-    <t>0.2717,0.1169,0.6769,0.0129</t>
-  </si>
-  <si>
-    <t>0.4228,0.7215,0.0035,0.0006</t>
-  </si>
-  <si>
-    <t>0.7940,0.3546,0.0035,0.0004</t>
-  </si>
-  <si>
-    <t>0.7851,0.3057,0.0162,0.0013</t>
-  </si>
-  <si>
-    <t>0.9378,0.0711,0.0090,0.0005</t>
-  </si>
-  <si>
-    <t>0.7043,0.3994,0.0089,0.0009</t>
-  </si>
-  <si>
-    <t>0.8041,0.0279,0.2300,0.0062</t>
-  </si>
-  <si>
-    <t>0.8625,0.0232,0.0682,0.0264</t>
-  </si>
-  <si>
-    <t>0.7990,0.0094,0.0273,0.1205</t>
-  </si>
-  <si>
-    <t>0.5427,0.0119,0.6399,0.0020</t>
-  </si>
-  <si>
-    <t>0.8012,0.0146,0.1711,0.0220</t>
-  </si>
-  <si>
-    <t>0.1452,0.0401,0.8207,0.0482</t>
-  </si>
-  <si>
-    <t>0.0271,0.1037,0.8949,0.0314</t>
-  </si>
-  <si>
-    <t>0.0185,0.0415,0.9546,0.0029</t>
-  </si>
-  <si>
-    <t>0.1505,0.0208,0.8813,0.0060</t>
-  </si>
-  <si>
-    <t>0.0720,0.0454,0.9177,0.0010</t>
-  </si>
-  <si>
-    <t>0.9978,0.0004,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9903,0.0061,0.0010,0.0006</t>
-  </si>
-  <si>
-    <t>0.9870,0.0119,0.0013,0.0004</t>
-  </si>
-  <si>
-    <t>0.9891,0.0104,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.9878,0.0043,0.0005,0.0019</t>
-  </si>
-  <si>
-    <t>0.9982,0.0009,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9873,0.0107,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.9984,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0120,0.0153,0.9837,0.0009</t>
-  </si>
-  <si>
-    <t>0.3864,0.0569,0.6810,0.0122</t>
-  </si>
-  <si>
-    <t>0.9370,0.0375,0.0197,0.0063</t>
-  </si>
-  <si>
-    <t>0.0599,0.0107,0.9520,0.0004</t>
-  </si>
-  <si>
-    <t>0.0004,0.0058,0.9976,0.0002</t>
-  </si>
-  <si>
-    <t>0.0080,0.0903,0.9568,0.0005</t>
-  </si>
-  <si>
-    <t>0.0005,0.0030,0.9983,0.0002</t>
-  </si>
-  <si>
-    <t>0.0286,0.0073,0.9632,0.0027</t>
-  </si>
-  <si>
-    <t>0.0003,0.0142,0.9977,0.0005</t>
-  </si>
-  <si>
-    <t>0.0622,0.0042,0.9490,0.0013</t>
-  </si>
-  <si>
-    <t>0.0402,0.2691,0.8583,0.0033</t>
-  </si>
-  <si>
-    <t>0.7316,0.0154,0.3554,0.0046</t>
-  </si>
-  <si>
-    <t>0.3634,0.0017,0.6372,0.0227</t>
-  </si>
-  <si>
-    <t>0.9627,0.0030,0.0170,0.0022</t>
-  </si>
-  <si>
-    <t>0.9943,0.0017,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9974,0.0010,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9976,0.0009,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9868,0.0097,0.0018,0.0004</t>
-  </si>
-  <si>
-    <t>0.9966,0.0010,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9660,0.0312,0.0066,0.0011</t>
-  </si>
-  <si>
-    <t>0.9975,0.0012,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9776,0.0143,0.0032,0.0025</t>
-  </si>
-  <si>
-    <t>0.0102,0.1144,0.9551,0.0008</t>
-  </si>
-  <si>
-    <t>0.0069,0.0176,0.9804,0.0024</t>
-  </si>
-  <si>
-    <t>0.0036,0.0203,0.9886,0.0008</t>
-  </si>
-  <si>
-    <t>0.0412,0.0035,0.9708,0.0002</t>
-  </si>
-  <si>
-    <t>0.0035,0.0022,0.9937,0.0010</t>
-  </si>
-  <si>
-    <t>0.1068,0.0152,0.8575,0.0493</t>
-  </si>
-  <si>
-    <t>0.1429,0.0552,0.8456,0.0220</t>
-  </si>
-  <si>
-    <t>0.0101,0.0043,0.7042,0.6025</t>
-  </si>
-  <si>
-    <t>0.7530,0.0007,0.0023,0.4385</t>
-  </si>
-  <si>
-    <t>0.0187,0.0168,0.0021,0.9907</t>
-  </si>
-  <si>
-    <t>0.1057,0.0060,0.0017,0.9653</t>
-  </si>
-  <si>
-    <t>0.0054,0.0001,0.0004,0.9974</t>
-  </si>
-  <si>
-    <t>0.0063,0.0006,0.0002,0.9975</t>
-  </si>
-  <si>
-    <t>0.7702,0.0073,0.0796,0.1084</t>
+    <t>0.0028,0.0017,0.9951,0.0009</t>
+  </si>
+  <si>
+    <t>0.0672,0.0567,0.8852,0.0053</t>
+  </si>
+  <si>
+    <t>0.5499,0.0259,0.5049,0.0118</t>
+  </si>
+  <si>
+    <t>0.0259,0.0009,0.9857,0.0002</t>
+  </si>
+  <si>
+    <t>0.0590,0.9298,0.0048,0.0038</t>
+  </si>
+  <si>
+    <t>0.0069,0.9834,0.0017,0.0018</t>
+  </si>
+  <si>
+    <t>0.2458,0.8050,0.0120,0.0021</t>
+  </si>
+  <si>
+    <t>0.1645,0.8626,0.0054,0.0032</t>
+  </si>
+  <si>
+    <t>0.0445,0.9448,0.0026,0.0042</t>
+  </si>
+  <si>
+    <t>0.0079,0.9827,0.0026,0.0017</t>
+  </si>
+  <si>
+    <t>0.6469,0.5137,0.0065,0.0009</t>
+  </si>
+  <si>
+    <t>0.7855,0.0787,0.1261,0.0154</t>
+  </si>
+  <si>
+    <t>0.1282,0.0259,0.8841,0.0056</t>
+  </si>
+  <si>
+    <t>0.6424,0.1484,0.2154,0.0225</t>
+  </si>
+  <si>
+    <t>0.7223,0.0264,0.3130,0.0045</t>
+  </si>
+  <si>
+    <t>0.4642,0.0496,0.0565,0.6380</t>
+  </si>
+  <si>
+    <t>0.0034,0.9839,0.0660,0.0008</t>
+  </si>
+  <si>
+    <t>0.0166,0.9597,0.0710,0.0058</t>
+  </si>
+  <si>
+    <t>0.0567,0.8608,0.0889,0.1028</t>
+  </si>
+  <si>
+    <t>0.0014,0.9283,0.8458,0.0012</t>
+  </si>
+  <si>
+    <t>0.0434,0.9381,0.0724,0.0004</t>
+  </si>
+  <si>
+    <t>0.7091,0.3603,0.0224,0.0023</t>
+  </si>
+  <si>
+    <t>0.7367,0.3095,0.0280,0.0036</t>
+  </si>
+  <si>
+    <t>0.9892,0.0053,0.0012,0.0012</t>
+  </si>
+  <si>
+    <t>0.9898,0.0021,0.0018,0.0021</t>
+  </si>
+  <si>
+    <t>0.9848,0.0059,0.0025,0.0029</t>
+  </si>
+  <si>
+    <t>0.9861,0.0023,0.0023,0.0031</t>
+  </si>
+  <si>
+    <t>0.9963,0.0004,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.8402,0.0157,0.1193,0.0112</t>
+  </si>
+  <si>
+    <t>0.9965,0.0003,0.0001,0.0015</t>
+  </si>
+  <si>
+    <t>0.9946,0.0009,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.0099,0.2013,0.9637,0.0017</t>
+  </si>
+  <si>
+    <t>0.0026,0.6215,0.8801,0.0000</t>
+  </si>
+  <si>
+    <t>0.0449,0.1341,0.9092,0.0022</t>
+  </si>
+  <si>
+    <t>0.0199,0.0638,0.9665,0.0002</t>
+  </si>
+  <si>
+    <t>0.4645,0.0310,0.4585,0.0935</t>
+  </si>
+  <si>
+    <t>0.8277,0.0116,0.1681,0.0149</t>
+  </si>
+  <si>
+    <t>0.3492,0.0013,0.7984,0.0041</t>
+  </si>
+  <si>
+    <t>0.5380,0.3778,0.1329,0.0255</t>
+  </si>
+  <si>
+    <t>0.1091,0.0005,0.0007,0.9708</t>
+  </si>
+  <si>
+    <t>0.0010,0.0003,0.0006,0.9990</t>
+  </si>
+  <si>
+    <t>0.0044,0.0698,0.0013,0.9944</t>
+  </si>
+  <si>
+    <t>0.0228,0.0003,0.0010,0.9909</t>
+  </si>
+  <si>
+    <t>0.0008,0.8135,0.6833,0.0147</t>
+  </si>
+  <si>
+    <t>0.9758,0.0090,0.0042,0.0048</t>
+  </si>
+  <si>
+    <t>0.5209,0.5505,0.0140,0.0104</t>
+  </si>
+  <si>
+    <t>0.9893,0.0036,0.0006,0.0015</t>
+  </si>
+  <si>
+    <t>0.6435,0.4139,0.0278,0.0081</t>
+  </si>
+  <si>
+    <t>0.9697,0.0066,0.0024,0.0101</t>
+  </si>
+  <si>
+    <t>0.2933,0.0309,0.0114,0.8183</t>
+  </si>
+  <si>
+    <t>0.9867,0.0067,0.0022,0.0014</t>
+  </si>
+  <si>
+    <t>0.0002,0.1194,0.9947,0.0018</t>
+  </si>
+  <si>
+    <t>0.8972,0.0005,0.0015,0.1502</t>
+  </si>
+  <si>
+    <t>0.9794,0.0004,0.0001,0.0212</t>
+  </si>
+  <si>
+    <t>0.1171,0.8630,0.0292,0.0208</t>
+  </si>
+  <si>
+    <t>0.9641,0.0128,0.0074,0.0019</t>
+  </si>
+  <si>
+    <t>0.9443,0.0333,0.0168,0.0010</t>
+  </si>
+  <si>
+    <t>0.2185,0.7663,0.0488,0.0176</t>
+  </si>
+  <si>
+    <t>0.9038,0.0625,0.0316,0.0018</t>
+  </si>
+  <si>
+    <t>0.8304,0.1327,0.0382,0.0029</t>
+  </si>
+  <si>
+    <t>0.9942,0.0019,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.9919,0.0021,0.0005,0.0016</t>
+  </si>
+  <si>
+    <t>0.9966,0.0008,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9965,0.0005,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9760,0.0132,0.0025,0.0025</t>
+  </si>
+  <si>
+    <t>0.9791,0.0209,0.0018,0.0008</t>
+  </si>
+  <si>
+    <t>0.9955,0.0014,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9911,0.0016,0.0006,0.0020</t>
+  </si>
+  <si>
+    <t>0.8337,0.2017,0.0062,0.0070</t>
+  </si>
+  <si>
+    <t>0.7963,0.2867,0.0126,0.0007</t>
+  </si>
+  <si>
+    <t>0.7572,0.3554,0.0068,0.0010</t>
+  </si>
+  <si>
+    <t>0.0248,0.5946,0.7951,0.0008</t>
+  </si>
+  <si>
+    <t>0.9399,0.0897,0.0045,0.0012</t>
+  </si>
+  <si>
+    <t>0.8281,0.0704,0.0930,0.0007</t>
+  </si>
+  <si>
+    <t>0.9910,0.0065,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9174,0.0885,0.0107,0.0011</t>
+  </si>
+  <si>
+    <t>0.0013,0.5576,0.9746,0.0001</t>
+  </si>
+  <si>
+    <t>0.8388,0.1855,0.0242,0.0029</t>
+  </si>
+  <si>
+    <t>0.0051,0.0095,0.9931,0.0002</t>
+  </si>
+  <si>
+    <t>0.0021,0.0228,0.9943,0.0004</t>
+  </si>
+  <si>
+    <t>0.1274,0.0108,0.8963,0.0057</t>
+  </si>
+  <si>
+    <t>0.0026,0.0756,0.9852,0.0017</t>
+  </si>
+  <si>
+    <t>0.0307,0.0148,0.9578,0.0031</t>
+  </si>
+  <si>
+    <t>0.0026,0.0054,0.9949,0.0001</t>
+  </si>
+  <si>
+    <t>0.0229,0.0016,0.9840,0.0004</t>
+  </si>
+  <si>
+    <t>0.4496,0.1003,0.5052,0.0385</t>
+  </si>
+  <si>
+    <t>0.2264,0.0111,0.8634,0.0007</t>
+  </si>
+  <si>
+    <t>0.7370,0.0675,0.2280,0.0272</t>
+  </si>
+  <si>
+    <t>0.1736,0.2797,0.4263,0.0008</t>
+  </si>
+  <si>
+    <t>0.0771,0.4705,0.5837,0.0038</t>
+  </si>
+  <si>
+    <t>0.2087,0.1102,0.7035,0.0056</t>
+  </si>
+  <si>
+    <t>0.4137,0.0377,0.6529,0.0174</t>
+  </si>
+  <si>
+    <t>0.5848,0.1180,0.3300,0.0325</t>
+  </si>
+  <si>
+    <t>0.8339,0.2645,0.0043,0.0003</t>
+  </si>
+  <si>
+    <t>0.7537,0.3764,0.0046,0.0004</t>
+  </si>
+  <si>
+    <t>0.7812,0.3118,0.0126,0.0007</t>
+  </si>
+  <si>
+    <t>0.9947,0.0021,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.8869,0.1520,0.0133,0.0010</t>
+  </si>
+  <si>
+    <t>0.5091,0.4032,0.0645,0.0591</t>
+  </si>
+  <si>
+    <t>0.8993,0.0093,0.0863,0.0062</t>
+  </si>
+  <si>
+    <t>0.8237,0.0308,0.0817,0.0473</t>
+  </si>
+  <si>
+    <t>0.6048,0.0146,0.5272,0.0050</t>
+  </si>
+  <si>
+    <t>0.6405,0.0202,0.4111,0.0155</t>
+  </si>
+  <si>
+    <t>0.0267,0.0255,0.9053,0.1285</t>
+  </si>
+  <si>
+    <t>0.0189,0.5973,0.8143,0.0181</t>
+  </si>
+  <si>
+    <t>0.0397,0.0091,0.9637,0.0022</t>
+  </si>
+  <si>
+    <t>0.0822,0.0413,0.9210,0.0047</t>
+  </si>
+  <si>
+    <t>0.0643,0.3077,0.7199,0.0051</t>
+  </si>
+  <si>
+    <t>0.9898,0.0028,0.0008,0.0020</t>
+  </si>
+  <si>
+    <t>0.9867,0.0100,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.9890,0.0055,0.0007,0.0013</t>
+  </si>
+  <si>
+    <t>0.9944,0.0026,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9903,0.0063,0.0014,0.0006</t>
+  </si>
+  <si>
+    <t>0.9884,0.0067,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.9840,0.0092,0.0018,0.0012</t>
+  </si>
+  <si>
+    <t>0.9959,0.0008,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.0109,0.0097,0.9823,0.0042</t>
+  </si>
+  <si>
+    <t>0.5976,0.1083,0.3728,0.0039</t>
+  </si>
+  <si>
+    <t>0.8465,0.0592,0.0815,0.0210</t>
+  </si>
+  <si>
+    <t>0.0048,0.0062,0.9942,0.0001</t>
+  </si>
+  <si>
+    <t>0.0018,0.0082,0.9930,0.0008</t>
+  </si>
+  <si>
+    <t>0.0174,0.0051,0.9813,0.0002</t>
+  </si>
+  <si>
+    <t>0.0033,0.0056,0.9953,0.0002</t>
+  </si>
+  <si>
+    <t>0.0405,0.0130,0.9429,0.0075</t>
+  </si>
+  <si>
+    <t>0.0107,0.0086,0.9859,0.0016</t>
+  </si>
+  <si>
+    <t>0.0057,0.0399,0.9832,0.0003</t>
+  </si>
+  <si>
+    <t>0.2747,0.0640,0.7142,0.0223</t>
+  </si>
+  <si>
+    <t>0.6851,0.0449,0.2262,0.0445</t>
+  </si>
+  <si>
+    <t>0.8748,0.0025,0.2169,0.0013</t>
+  </si>
+  <si>
+    <t>0.9262,0.0044,0.0474,0.0067</t>
+  </si>
+  <si>
+    <t>0.9959,0.0008,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9830,0.0137,0.0024,0.0006</t>
+  </si>
+  <si>
+    <t>0.9954,0.0031,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9580,0.0430,0.0067,0.0015</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9823,0.0193,0.0018,0.0003</t>
+  </si>
+  <si>
+    <t>0.9913,0.0079,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9926,0.0025,0.0007,0.0010</t>
+  </si>
+  <si>
+    <t>0.0392,0.1202,0.8110,0.0034</t>
+  </si>
+  <si>
+    <t>0.0055,0.0376,0.9774,0.0026</t>
+  </si>
+  <si>
+    <t>0.0336,0.0324,0.9341,0.0047</t>
+  </si>
+  <si>
+    <t>0.0513,0.0071,0.9486,0.0020</t>
+  </si>
+  <si>
+    <t>0.0086,0.0031,0.9841,0.0038</t>
+  </si>
+  <si>
+    <t>0.2528,0.0421,0.7627,0.0343</t>
+  </si>
+  <si>
+    <t>0.0366,0.0365,0.9378,0.0079</t>
+  </si>
+  <si>
+    <t>0.0077,0.1408,0.9513,0.0181</t>
+  </si>
+  <si>
+    <t>0.5210,0.0098,0.0391,0.5318</t>
+  </si>
+  <si>
+    <t>0.0061,0.0496,0.0006,0.9934</t>
+  </si>
+  <si>
+    <t>0.2199,0.0072,0.0039,0.9040</t>
+  </si>
+  <si>
+    <t>0.0139,0.0001,0.0003,0.9958</t>
+  </si>
+  <si>
+    <t>0.0164,0.0004,0.0003,0.9946</t>
+  </si>
+  <si>
+    <t>0.4550,0.0527,0.0078,0.6318</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2136,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2276,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2287,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2374,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2385,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2413,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2444,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2455,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2483,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,7 +2584,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,10 +2819,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2931,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2973,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,10 +2987,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3087,10 +3099,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3127,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3141,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3158,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,10 +3169,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,10 +3435,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3547,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3592,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3606,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3620,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3676,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3718,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3841,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3858,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3885,10 +3897,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,10 +3911,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3928,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4037,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4065,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4096,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4163,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4205,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4362,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4373,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4387,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4401,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4459,10 +4471,10 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4600,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4628,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4667,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4681,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4695,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4709,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4726,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4821,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4863,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5199,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5412,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,10 +5437,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5451,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,10 +5521,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
